--- a/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
+++ b/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R5f8e5ed6bb97431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="2" r:id="R4e4ec62a2ac148f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="3" r:id="Rd835e98351e54c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="4" r:id="R168328cfe81848de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="5" r:id="R7faea91bcbdf460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formula Reference" sheetId="6" r:id="R16544a47ee304e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rff006912c59144b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="2" r:id="Rb5bb44497ffa41b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="3" r:id="R3aaec0166f214d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="4" r:id="R58ce96e9929c4d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="5" r:id="Ra0a5325689aa4dfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formula Reference" sheetId="6" r:id="Re4ddcde63a3e4666"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2380,9 +2380,7 @@
       <x:c r="G4" t="str">
         <x:v>Tidal North Kitchen sales</x:v>
       </x:c>
-      <x:c r="H4" t="str">
-        <x:v>H5</x:v>
-      </x:c>
+      <x:c r="H4"/>
       <x:c r="I4" t="str">
         <x:v>SUMIFS</x:v>
       </x:c>
@@ -2407,14 +2405,13 @@
       <x:c r="G5" t="str">
         <x:v>Harborside open records</x:v>
       </x:c>
-      <x:c r="H5" t="str">
-        <x:v>H6</x:v>
-      </x:c>
+      <x:c r="H5"/>
       <x:c r="I5" t="str">
         <x:v>COUNTIFS</x:v>
       </x:c>
-      <x:c r="J5" t="e">
+      <x:c r="J5" t="str">
         <x:f>IF(H5="","Enter formula",IF(ABS(H5-SUMIFS('Raw Data'!H:H,'Raw Data'!D:D,"Kitchen",'Raw Data'!F:F,"North"))&lt;0.01,"Looks right","Check SUMIFS criteria"))</x:f>
+        <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2436,15 +2433,13 @@
       <x:c r="G6" t="str">
         <x:v>Meridian overtime flag for MA-103</x:v>
       </x:c>
-      <x:c r="H6" t="str">
-        <x:v>H7</x:v>
-      </x:c>
+      <x:c r="H6"/>
       <x:c r="I6" t="str">
         <x:v>IF</x:v>
       </x:c>
       <x:c r="J6" t="str">
         <x:f>IF(H6="","Enter formula",IF(H6=COUNTIFS('Raw Data'!A:A,"Harborside Medical Center",'Raw Data'!G:G,"Open"),"Looks right","Check COUNTIFS criteria"))</x:f>
-        <x:v>Check COUNTIFS criteria</x:v>
+        <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2466,15 +2461,13 @@
       <x:c r="G7" t="str">
         <x:v>Last day of current month</x:v>
       </x:c>
-      <x:c r="H7" t="str">
-        <x:v>H8</x:v>
-      </x:c>
+      <x:c r="H7"/>
       <x:c r="I7" t="str">
         <x:v>EOMONTH</x:v>
       </x:c>
       <x:c r="J7" t="str">
         <x:f>IF(H7="","Enter formula",IF(H7="Overtime","Looks right","IF should flag &gt;40 hours"))</x:f>
-        <x:v>IF should flag &gt;40 hours</x:v>
+        <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2496,15 +2489,13 @@
       <x:c r="G8" t="str">
         <x:v>Text label: Company - Category - Region for first raw row</x:v>
       </x:c>
-      <x:c r="H8" t="str">
-        <x:v>H9</x:v>
-      </x:c>
+      <x:c r="H8"/>
       <x:c r="I8" t="str">
         <x:v>TEXTJOIN</x:v>
       </x:c>
       <x:c r="J8" t="str">
         <x:f>IF(H8="","Enter formula",IF(H8=EOMONTH(TODAY(),0),"Looks right","Use EOMONTH(TODAY(),0)"))</x:f>
-        <x:v>Use EOMONTH(TODAY(),0)</x:v>
+        <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
     <x:row r="9">

--- a/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
+++ b/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
@@ -2,36 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rff006912c59144b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="2" r:id="Rb5bb44497ffa41b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="3" r:id="R3aaec0166f214d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="4" r:id="R58ce96e9929c4d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="5" r:id="Ra0a5325689aa4dfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formula Reference" sheetId="6" r:id="Re4ddcde63a3e4666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R35974cdbe7b24267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="2" r:id="R103955ad785c4a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="3" r:id="R020e93e9e6a544b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="4" r:id="R796c07ddeefd4e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="5" r:id="R8d3120c8a9a84063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formula Reference" sheetId="6" r:id="Reffd487f15894c75"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/metadata1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:metadata xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:metadataTypes count="1">
-    <x:metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </x:metadataTypes>
-  <x:futureMetadata name="XLDAPR" count="1">
-    <x:bk>
-      <x:extLst>
-        <x:ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" fDynamic="1" fCollapsed="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:bk>
-  </x:futureMetadata>
-  <x:cellMetadata count="1">
-    <x:bk>
-      <x:rc t="1" v="0"/>
-    </x:bk>
-  </x:cellMetadata>
-</x:metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2384,7 +2362,10 @@
       <x:c r="I4" t="str">
         <x:v>SUMIFS</x:v>
       </x:c>
-      <x:c r="J4"/>
+      <x:c r="J4" t="str">
+        <x:f>IF(H4="","Enter formula",IF(ABS(H4-SUMIFS('Raw Data'!H:H,'Raw Data'!D:D,"Kitchen",'Raw Data'!F:F,"North"))&lt;0.01,"Looks right","Check SUMIFS criteria"))</x:f>
+        <x:v>Enter formula</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -2410,7 +2391,7 @@
         <x:v>COUNTIFS</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:f>IF(H5="","Enter formula",IF(ABS(H5-SUMIFS('Raw Data'!H:H,'Raw Data'!D:D,"Kitchen",'Raw Data'!F:F,"North"))&lt;0.01,"Looks right","Check SUMIFS criteria"))</x:f>
+        <x:f>IF(H5="","Enter formula",IF(H5=COUNTIFS('Raw Data'!A:A,"Harborside Medical Center",'Raw Data'!G:G,"Open"),"Looks right","Check COUNTIFS criteria"))</x:f>
         <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
@@ -2438,7 +2419,7 @@
         <x:v>IF</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:f>IF(H6="","Enter formula",IF(H6=COUNTIFS('Raw Data'!A:A,"Harborside Medical Center",'Raw Data'!G:G,"Open"),"Looks right","Check COUNTIFS criteria"))</x:f>
+        <x:f>IF(H6="","Enter formula",IF(H6="Overtime","Looks right","IF should flag &gt;40 hours"))</x:f>
         <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
@@ -2466,7 +2447,7 @@
         <x:v>EOMONTH</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:f>IF(H7="","Enter formula",IF(H7="Overtime","Looks right","IF should flag &gt;40 hours"))</x:f>
+        <x:f>IF(H7="","Enter formula",IF(H7=EOMONTH(TODAY(),0),"Looks right","Use EOMONTH(TODAY(),0)"))</x:f>
         <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
@@ -2494,7 +2475,7 @@
         <x:v>TEXTJOIN</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:f>IF(H8="","Enter formula",IF(H8=EOMONTH(TODAY(),0),"Looks right","Use EOMONTH(TODAY(),0)"))</x:f>
+        <x:f>IF(H8="","Enter formula",IF(H8="Anchor &amp; Oak Events - Wedding - North","Looks right","Check TEXTJOIN delimiter and source cells"))</x:f>
         <x:v>Enter formula</x:v>
       </x:c>
     </x:row>
@@ -2507,10 +2488,7 @@
       <x:c r="G9" t="str"/>
       <x:c r="H9" t="str"/>
       <x:c r="I9" t="str"/>
-      <x:c r="J9" t="str">
-        <x:f>IF(H9="","Enter formula",IF(H9="Anchor &amp; Oak Events - Wedding - North","Looks right","Check TEXTJOIN delimiter and source cells"))</x:f>
-        <x:v>Enter formula</x:v>
-      </x:c>
+      <x:c r="J9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -2642,8 +2620,8 @@
       <x:c r="A4" t="str">
         <x:v>SUM</x:v>
       </x:c>
-      <x:c r="B4" t="e">
-        <x:f>SUM(range)</x:f>
+      <x:c r="B4" t="str">
+        <x:v>=SUM(range)</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>What is the total?</x:v>
@@ -2659,8 +2637,8 @@
       <x:c r="A5" t="str">
         <x:v>AVERAGE</x:v>
       </x:c>
-      <x:c r="B5" t="e">
-        <x:f>AVERAGE(range)</x:f>
+      <x:c r="B5" t="str">
+        <x:v>=AVERAGE(range)</x:v>
       </x:c>
       <x:c r="C5" t="str">
         <x:v>What is typical?</x:v>
@@ -2676,8 +2654,8 @@
       <x:c r="A6" t="str">
         <x:v>MAX</x:v>
       </x:c>
-      <x:c r="B6" t="e">
-        <x:f>MAX(range)</x:f>
+      <x:c r="B6" t="str">
+        <x:v>=MAX(range)</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>What is highest?</x:v>
@@ -2693,8 +2671,8 @@
       <x:c r="A7" t="str">
         <x:v>MIN</x:v>
       </x:c>
-      <x:c r="B7" t="e">
-        <x:f>MIN(range)</x:f>
+      <x:c r="B7" t="str">
+        <x:v>=MIN(range)</x:v>
       </x:c>
       <x:c r="C7" t="str">
         <x:v>What is lowest?</x:v>
@@ -2710,9 +2688,8 @@
       <x:c r="A8" t="str">
         <x:v>COUNT</x:v>
       </x:c>
-      <x:c r="B8" t="n">
-        <x:f>COUNT(range)</x:f>
-        <x:v>0</x:v>
+      <x:c r="B8" t="str">
+        <x:v>=COUNT(range)</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>How many numeric cells?</x:v>
@@ -2728,9 +2705,8 @@
       <x:c r="A9" t="str">
         <x:v>COUNTA</x:v>
       </x:c>
-      <x:c r="B9" t="n">
-        <x:f>COUNTA(range)</x:f>
-        <x:v>1</x:v>
+      <x:c r="B9" t="str">
+        <x:v>=COUNTA(range)</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>How many non-empty cells?</x:v>
@@ -2746,8 +2722,8 @@
       <x:c r="A10" t="str">
         <x:v>IF</x:v>
       </x:c>
-      <x:c r="B10" t="e">
-        <x:f>IF(test,true,false)</x:f>
+      <x:c r="B10" t="str">
+        <x:v>=IF(test,true,false)</x:v>
       </x:c>
       <x:c r="C10" t="str">
         <x:v>Which result should appear?</x:v>
@@ -2763,8 +2739,8 @@
       <x:c r="A11" t="str">
         <x:v>AND</x:v>
       </x:c>
-      <x:c r="B11" t="e">
-        <x:f>AND(test1,test2)</x:f>
+      <x:c r="B11" t="str">
+        <x:v>=AND(test1,test2)</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>Are all conditions true?</x:v>
@@ -2780,8 +2756,8 @@
       <x:c r="A12" t="str">
         <x:v>OR</x:v>
       </x:c>
-      <x:c r="B12" t="e">
-        <x:f>OR(test1,test2)</x:f>
+      <x:c r="B12" t="str">
+        <x:v>=OR(test1,test2)</x:v>
       </x:c>
       <x:c r="C12" t="str">
         <x:v>Is any condition true?</x:v>
@@ -2797,8 +2773,8 @@
       <x:c r="A13" t="str">
         <x:v>SUMIFS</x:v>
       </x:c>
-      <x:c r="B13" t="e">
-        <x:f>SUMIFS(sum_range,criteria_range,criteria)</x:f>
+      <x:c r="B13" t="str">
+        <x:v>=SUMIFS(sum_range,criteria_range,criteria)</x:v>
       </x:c>
       <x:c r="C13" t="str">
         <x:v>What total meets criteria?</x:v>
@@ -2814,9 +2790,8 @@
       <x:c r="A14" t="str">
         <x:v>COUNTIFS</x:v>
       </x:c>
-      <x:c r="B14" t="n">
-        <x:f>COUNTIFS(criteria_range,criteria)</x:f>
-        <x:v>1</x:v>
+      <x:c r="B14" t="str">
+        <x:v>=COUNTIFS(criteria_range,criteria)</x:v>
       </x:c>
       <x:c r="C14" t="str">
         <x:v>How many rows meet criteria?</x:v>
@@ -2832,8 +2807,8 @@
       <x:c r="A15" t="str">
         <x:v>XLOOKUP</x:v>
       </x:c>
-      <x:c r="B15" t="e">
-        <x:f>XLOOKUP(value,lookup_array,return_array,if_not_found)</x:f>
+      <x:c r="B15" t="str">
+        <x:v>=XLOOKUP(value,lookup_array,return_array,if_not_found)</x:v>
       </x:c>
       <x:c r="C15" t="str">
         <x:v>What matching value belongs to this ID?</x:v>
@@ -2849,8 +2824,8 @@
       <x:c r="A16" t="str">
         <x:v>FILTER</x:v>
       </x:c>
-      <x:c r="B16" t="e">
-        <x:f>FILTER(array,include,if_empty)</x:f>
+      <x:c r="B16" t="str">
+        <x:v>=FILTER(array,include,if_empty)</x:v>
       </x:c>
       <x:c r="C16" t="str">
         <x:v>Which rows match?</x:v>
@@ -2866,8 +2841,8 @@
       <x:c r="A17" t="str">
         <x:v>UNIQUE</x:v>
       </x:c>
-      <x:c r="B17" t="e" cm="1">
-        <x:f t="array" ref="B17">UNIQUE(range)</x:f>
+      <x:c r="B17" t="str">
+        <x:v>=UNIQUE(range)</x:v>
       </x:c>
       <x:c r="C17" t="str">
         <x:v>What are the distinct values?</x:v>
@@ -2883,8 +2858,8 @@
       <x:c r="A18" t="str">
         <x:v>SORT</x:v>
       </x:c>
-      <x:c r="B18" t="e" cm="1">
-        <x:f t="array" ref="B18">_xlfn._xlws.SORT(array)</x:f>
+      <x:c r="B18" t="str">
+        <x:v>=SORT(array)</x:v>
       </x:c>
       <x:c r="C18" t="str">
         <x:v>How should the list be ordered?</x:v>
@@ -2900,8 +2875,8 @@
       <x:c r="A19" t="str">
         <x:v>SEQUENCE</x:v>
       </x:c>
-      <x:c r="B19" t="e">
-        <x:f>SEQUENCE(rows)</x:f>
+      <x:c r="B19" t="str">
+        <x:v>=SEQUENCE(rows)</x:v>
       </x:c>
       <x:c r="C19" t="str">
         <x:v>Can Excel generate the list?</x:v>
@@ -2917,8 +2892,8 @@
       <x:c r="A20" t="str">
         <x:v>EOMONTH</x:v>
       </x:c>
-      <x:c r="B20" t="e">
-        <x:f>EOMONTH(date,months)</x:f>
+      <x:c r="B20" t="str">
+        <x:v>=EOMONTH(date,months)</x:v>
       </x:c>
       <x:c r="C20" t="str">
         <x:v>What is the month end?</x:v>

--- a/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
+++ b/EXCEL/M03/bus123-excel-m03-l01-starter.xlsx
@@ -5,10 +5,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Functions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic Arrays" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting Lab" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -16,8 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -39,8 +45,45 @@
       <color rgb="FF355773"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00B8843D"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="004A5567"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="001A1F2C"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00355773"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -87,8 +130,48 @@
         <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A7C5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C4A2B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -104,11 +187,67 @@
         <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9B458"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9B458"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9B458"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9B458"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="004A7C5E"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9D18E"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9D18E"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9D18E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9D18E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +289,58 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -379,6 +570,9 @@
   </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -394,7 +588,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -407,42 +600,41 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Student Tasks</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1. Complete Core Functions yellow cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2. Use Dynamic Arrays to create spill ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3. Use XLOOKUP, SUMIFS, COUNTIFS, and IF in Reporting Lab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4. Answer the reflection prompts in each sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>1. Open Live You Try It during the slide pauses. Enter the slide givens into yellow cells first, then build formulas from those cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>2. Use Raw Data, Core Functions, Dynamic Arrays, and Reporting Lab as additional practice for choosing Excel functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>3. Complete Class Challenge as the graded / next-level activity. Scenario text gives the required inputs; yellow input cells and blue final-answer cells start blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>4. Use the FormulaReferenceCard only as a syntax reminder after you have tried the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1"/>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Case Companies</t>
@@ -464,15 +656,15 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="26" customHeight="1">
       <c r="B12" t="inlineStr">
         <is>
           <t>Meridian Advisory Group</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
+    <row r="13" ht="26" customHeight="1"/>
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Color Guide</t>
@@ -480,26 +672,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yellow cells are student formula cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>Yellow cells are student input cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Green cells contain feedback checks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>Blue cells are student final answer cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue tables are source data. Do not overwrite Raw Data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
+          <t>Green cells contain self-check feedback formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1"/>
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>Submission Reminder</t>
@@ -511,19 +703,29 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
+    <row r="19" ht="26" customHeight="1"/>
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>This workbook intentionally uses only student-facing data. It does not contain answer keys or hidden grading notes.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>This workbook intentionally uses only student-facing data. It does not contain answer keys, grading maps, or hidden instructor notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1"/>
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Start with the Raw Data tab, then move left to right through the workbook.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Suggested flow: START HERE, Raw Data, Live You Try It, existing practice tabs, Class Challenge, FormulaReferenceCard.</t>
         </is>
       </c>
     </row>
@@ -1794,421 +1996,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Anchor &amp; Oak Events - Core Summary Functions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SUM Running Total</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Average Check</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Student Formula Notes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Student Formula Cell</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Expected Skill</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>EXCEL-M03-L01 - Live You Try It</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Self-graded Excel pauses. Enter slide givens into yellow cells first, then build formulas using cell references.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>35700</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Annual revenue total</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Practice Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Pause</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Slide</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Build This</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Input 1</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Input 2</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Input 3</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Input 4</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Input 5</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Input 6</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>Your Formula / Answer</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>Formula Hint</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>21400</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Average monthly revenue</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>29500</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Best month revenue</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>MAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>43300</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Slowest month revenue</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>B21</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>54600</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Number of numeric months</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>B22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>COUNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>67200</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Number of month labels</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>B23</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>COUNTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>74500</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>63800</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>47200</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>40400</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>38600</v>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Use the six visible Anchor &amp; Oak monthly revenues to total Jan-Jun revenue.</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="28" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>Reference all six yellow revenue cells with SUM.</t>
+        </is>
+      </c>
+      <c r="L7" s="31">
+        <f>IF(J7="","Enter the SUM formula.",IF(ABS(J7-251700)&lt;0.01,"Correct - Jan-Jun revenue totals 251,700.","Check that all six slide values are included."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>SUMIFS</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Use the Tidal sales rows to total Kitchen sales in the North region.</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>Kitchen North appears in the first and fourth slide rows.</t>
+        </is>
+      </c>
+      <c r="L8" s="31">
+        <f>IF(J8="","Enter a formula.",IF(ABS(J8-14600)&lt;0.01,"Correct - Kitchen North sales total 14,600.","Check which rows are both Kitchen and North."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>XLOOKUP</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Use the employee table to return the name for employee M102.</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="32" t="n"/>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>Put IDs in one lookup row and names in the row beside each ID.</t>
+        </is>
+      </c>
+      <c r="L9" s="31">
+        <f>IF(J9="","Enter the XLOOKUP formula.",IF(J9="Blake","Correct - M102 returns Blake.","Check the lookup and return ranges."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Create shift numbers 1 through 12, then total the generated sequence.</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="33" t="n"/>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>A sequence from 1 through 12 totals 78.</t>
+        </is>
+      </c>
+      <c r="L10" s="31">
+        <f>IF(J10="","Enter a formula using SEQUENCE.",IF(J10=78,"Correct - the 1 to 12 sequence totals 78.","Check the sequence length."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>SUMPRODUCT</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Calculate total inventory value for Tote, Mug, and Apron.</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="29" t="n"/>
+      <c r="K11" s="30" t="inlineStr">
+        <is>
+          <t>Multiply quantity by cost for each item, then add the products.</t>
+        </is>
+      </c>
+      <c r="L11" s="31">
+        <f>IF(J11="","Enter the SUMPRODUCT-style formula.",IF(ABS(J11-939)&lt;0.01,"Correct - total inventory value is 939.","Check each quantity times cost pair."))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>ROUND</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Round the messy report number to two decimal places.</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>ROUND needs the number first and digits second.</t>
+        </is>
+      </c>
+      <c r="L12" s="31">
+        <f>IF(J12="","Enter the ROUND formula.",IF(ABS(J12-13.75)&lt;0.001,"Correct - the rounded value is 13.75.","Check the digits argument."))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>51200</v>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Self-check score</t>
+        </is>
+      </c>
+      <c r="B15" s="36">
+        <f>COUNTIF(L7:L12,"Correct*")&amp;" of 6 complete"</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Summary Question</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Student Formula</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Feedback Check</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Annual revenue total</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SUM check</t>
-        </is>
-      </c>
-      <c r="E18">
-        <f>IF(B18="","Enter a formula",IF(ABS(B18-SUM(B4:B15))&lt;0.01,"Looks right","Check SUM range"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Average monthly revenue</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AVERAGE check</t>
-        </is>
-      </c>
-      <c r="E19">
-        <f>IF(B19="","Enter a formula",IF(ABS(B19-AVERAGE(B4:B15))&lt;0.01,"Looks right","Check AVERAGE range"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Best month revenue</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MAX check</t>
-        </is>
-      </c>
-      <c r="E20">
-        <f>IF(B20="","Enter a formula",IF(ABS(B20-MAX(B4:B15))&lt;0.01,"Looks right","Check MAX range"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Slowest month revenue</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MIN check</t>
-        </is>
-      </c>
-      <c r="E21">
-        <f>IF(B21="","Enter a formula",IF(ABS(B21-MIN(B4:B15))&lt;0.01,"Looks right","Check MIN range"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Number of numeric months</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>COUNT check</t>
-        </is>
-      </c>
-      <c r="E22">
-        <f>IF(B22="","Enter a formula",IF(B22=COUNT(B4:B15),"Looks right","COUNT should count numeric cells"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Number of month labels</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>COUNTA check</t>
-        </is>
-      </c>
-      <c r="E23">
-        <f>IF(B23="","Enter a formula",IF(B23=COUNTA(A4:A15),"Looks right","COUNTA should count month labels"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Reflection Prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Which summary function best answers: "What is a normal month for Anchor &amp; Oak?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Which month would you investigate first if you were managing staffing?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>What formula risk appears if a student includes the header row?</t>
-        </is>
-      </c>
-    </row>
+          <t>Reminder</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>This tab is self-graded practice only. The private rubric does not grade Live You Try It.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="3">
+    <mergeCell ref="B17:L18"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2218,45 +2334,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Dynamic Arrays and Spill Practice</t>
+          <t>Anchor &amp; Oak Events - Core Summary Functions</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Record ID</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>SUM Running Total</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Average Check</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Student Formula Notes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2266,1054 +2382,374 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Anchor Cell</t>
+          <t>Student Formula Cell</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Formula Goal</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Student Notes</t>
+          <t>Expected Skill</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AO-001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="B4" t="n">
         <v>35700</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Unique company list</t>
+          <t>Annual revenue total</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Use UNIQUE on Company column</t>
+          <t>SUM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AO-002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="B5" t="n">
         <v>21400</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sorted category list</t>
+          <t>Average monthly revenue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>H23</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Use SORT and UNIQUE on Category column</t>
+          <t>AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AO-003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="B6" t="n">
         <v>29500</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Filter high balances</t>
+          <t>Best month revenue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>H32</t>
+          <t>B20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Use FILTER for Harborside amounts above 500</t>
+          <t>MAX</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AO-004</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B7" t="n">
         <v>43300</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Generate month numbers</t>
+          <t>Slowest month revenue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>H43</t>
+          <t>B21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Use SEQUENCE for 12 months</t>
+          <t>MIN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AO-005</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="B8" t="n">
         <v>54600</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reference a spill</t>
+          <t>Number of numeric months</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>J16</t>
+          <t>B22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Use H16# in another formula or note</t>
+          <t>COUNT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AO-006</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="B9" t="n">
         <v>67200</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Number of month labels</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>COUNTA</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AO-007</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="B10" t="n">
         <v>74500</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Reminder</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Spill ranges need empty cells below/right.</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AO-008</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="B11" t="n">
         <v>63800</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Hash sign</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Use the first spill cell plus #, such as H16#.</t>
-        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AO-009</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="B12" t="n">
         <v>47200</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>If you get #SPILL!</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Look for blocked cells in the output area.</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AO-010</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="B13" t="n">
         <v>40400</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Do not type results manually.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Let Excel spill.</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AO-011</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="B14" t="n">
         <v>38600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anchor &amp; Oak Events</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AO-012</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="B15" t="n">
         <v>51200</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Unique Companies - type formula in H16</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tidal Goods Co.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TG-001</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>8400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tidal Goods Co.</t>
+          <t>Summary Question</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TG-002</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Jan</t>
+          <t>Student Formula</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Feedback Check</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>5100</v>
+          <t>Result</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tidal Goods Co.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TG-003</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
+          <t>Annual revenue total</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>3900</v>
+          <t>SUM check</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>IF(B18="","Enter a formula",IF(ABS(B18-SUM(B4:B15))&lt;0.01,"Looks right","Check SUM range"))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tidal Goods Co.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TG-004</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
+          <t>Average monthly revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>6200</v>
+          <t>AVERAGE check</t>
+        </is>
+      </c>
+      <c r="E19">
+        <f>IF(B19="","Enter a formula",IF(ABS(B19-AVERAGE(B4:B15))&lt;0.01,"Looks right","Check AVERAGE range"))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tidal Goods Co.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TG-005</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
+          <t>Best month revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Outdoor</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>7600</v>
+          <t>MAX check</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>IF(B20="","Enter a formula",IF(ABS(B20-MAX(B4:B15))&lt;0.01,"Looks right","Check MAX range"))</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tidal Goods Co.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TG-006</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
+          <t>Slowest month revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>4100</v>
+          <t>MIN check</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>IF(B21="","Enter a formula",IF(ABS(B21-MIN(B4:B15))&lt;0.01,"Looks right","Check MIN range"))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HM-001</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
+          <t>Number of numeric months</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Medicare</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>620</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sorted Categories - type formula in H23</t>
-        </is>
+          <t>COUNT check</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>IF(B22="","Enter a formula",IF(B22=COUNT(B4:B15),"Looks right","COUNT should count numeric cells"))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HM-002</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
+          <t>Number of month labels</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HM-003</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Medicaid</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>780</v>
+          <t>COUNTA check</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>IF(B23="","Enter a formula",IF(B23=COUNTA(A4:A15),"Looks right","COUNTA should count month labels"))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HM-004</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Medicare</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>510</v>
+          <t>Reflection Prompt</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>HM-005</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>940</v>
+          <t>Which summary function best answers: "What is a normal month for Anchor &amp; Oak?"</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Harborside Medical Center</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>HM-006</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Medicare</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>450</v>
+          <t>Which month would you investigate first if you were managing staffing?</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MA-001</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MA-002</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MA-003</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Benefits</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MA-004</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>6100</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Harborside Open Balances Above $500 - type formula in H32</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>MA-005</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>7300</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Meridian Advisory Group</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MA-006</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Benefits</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Month Numbers - type formula in H43</t>
+          <t>What formula risk appears if a student includes the header row?</t>
         </is>
       </c>
     </row>
@@ -3328,340 +2764,1143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Reporting Lab - Choose the Function for the Business Question</t>
+          <t>Dynamic Arrays and Spill Practice</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Record ID</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hourly Rate</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hours Worked</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Question</t>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Amount</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Formula Cell</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Expected Function</t>
+          <t>Anchor Cell</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Formula Goal</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Student Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MA-101</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Avery Chen</t>
+          <t>AO-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>32</v>
-      </c>
-      <c r="E4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tidal North Kitchen sales</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>35700</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unique company list</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUMIFS</t>
-        </is>
-      </c>
-      <c r="J4">
-        <f>IF(H4="","Enter formula",IF(ABS(H4-SUMIFS('Raw Data'!H:H,'Raw Data'!D:D,"Kitchen",'Raw Data'!F:F,"North"))&lt;0.01,"Looks right","Check SUMIFS criteria"))</f>
-        <v/>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Use UNIQUE on Company column</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MA-102</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blake Ortiz</t>
+          <t>AO-002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Benefits</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>29</v>
-      </c>
-      <c r="E5" t="n">
-        <v>41</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Harborside open records</t>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>21400</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sorted category list</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COUNTIFS</t>
-        </is>
-      </c>
-      <c r="J5">
-        <f>IF(H5="","Enter formula",IF(H5=COUNTIFS('Raw Data'!A:A,"Harborside Medical Center",'Raw Data'!G:G,"Open"),"Looks right","Check COUNTIFS criteria"))</f>
-        <v/>
+          <t>H23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Use SORT and UNIQUE on Category column</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MA-103</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Casey Patel</t>
+          <t>AO-003</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Meridian overtime flag for MA-103</t>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Filter high balances</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IF</t>
-        </is>
-      </c>
-      <c r="J6">
-        <f>IF(H6="","Enter formula",IF(H6="Overtime","Looks right","IF should flag &gt;40 hours"))</f>
-        <v/>
+          <t>H32</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Use FILTER for Harborside amounts above 500</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MA-104</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Devon Reed</t>
+          <t>AO-004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>40</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Last day of current month</t>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>43300</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Generate month numbers</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EOMONTH</t>
-        </is>
-      </c>
-      <c r="J7">
-        <f>IF(H7="","Enter formula",IF(H7=EOMONTH(TODAY(),0),"Looks right","Use EOMONTH(TODAY(),0)"))</f>
-        <v/>
+          <t>H43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Use SEQUENCE for 12 months</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MA-105</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emery Silva</t>
+          <t>AO-005</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Benefits</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>28</v>
-      </c>
-      <c r="E8" t="n">
-        <v>35</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Text label: Company - Category - Region for first raw row</t>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>54600</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reference a spill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TEXTJOIN</t>
-        </is>
-      </c>
-      <c r="J8">
-        <f>IF(H8="","Enter formula",IF(H8="Anchor &amp; Oak Events - Wedding - North","Looks right","Check TEXTJOIN delimiter and source cells"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Use H16# in another formula or note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AO-006</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>67200</v>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lookup ID</t>
+          <t>Anchor &amp; Oak Events</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Student Formula</t>
+          <t>AO-007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Expected Function</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Hints</t>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>74500</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Reminder</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Spill ranges need empty cells below/right.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MA-103</t>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AO-008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>XLOOKUP</t>
-        </is>
-      </c>
-      <c r="D11">
-        <f>IF(B11="","Enter formula",IF(B11="Casey Patel","Looks right","Check XLOOKUP lookup and return arrays"))</f>
-        <v/>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SUMIFS total uses Raw Data Amount as sum range.</t>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>63800</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hash sign</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Use the first spill cell plus #, such as H16#.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MA-999</t>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AO-009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>XLOOKUP with if_not_found</t>
-        </is>
-      </c>
-      <c r="D12">
-        <f>IF(B12="","Enter formula",IF(B12="Check ID","Looks right","Use if_not_found message: Check ID"))</f>
-        <v/>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>COUNTIFS counts rows meeting multiple conditions.</t>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>47200</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>If you get #SPILL!</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Look for blocked cells in the output area.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IF should return Overtime when hours are greater than 40.</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AO-010</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>40400</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Do not type results manually.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Let Excel spill.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>TEXTJOIN should include delimiter and ignore blanks.</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AO-011</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>38600</v>
       </c>
     </row>
     <row r="15">
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Write formulas in the yellow Formula Cell references.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Anchor &amp; Oak Events</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AO-012</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>51200</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unique Companies - type formula in H16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TG-001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TG-002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5100</v>
+      </c>
+      <c r="H17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TG-003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TG-004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TG-005</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>7600</v>
+      </c>
+      <c r="H20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tidal Goods Co.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TG-006</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4100</v>
+      </c>
+      <c r="H21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HM-001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>620</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sorted Categories - type formula in H23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HM-002</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>240</v>
+      </c>
+      <c r="H23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HM-003</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Medicaid</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>780</v>
+      </c>
+      <c r="H24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HM-004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>510</v>
+      </c>
+      <c r="H25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HM-005</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>940</v>
+      </c>
+      <c r="H26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Harborside Medical Center</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HM-006</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>450</v>
+      </c>
+      <c r="H27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MA-001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MA-002</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MA-003</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MA-004</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6100</v>
+      </c>
+      <c r="H31" s="28" t="inlineStr">
+        <is>
+          <t>Harborside Open Balances Above $500 - type formula in H32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MA-005</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>7300</v>
+      </c>
+      <c r="H32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Meridian Advisory Group</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MA-006</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H33" s="28" t="n"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="H35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="H38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="H39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="H40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="28" t="n"/>
+    </row>
+    <row r="42">
+      <c r="H42" s="28" t="inlineStr">
+        <is>
+          <t>Month Numbers - type formula in H43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3673,7 +3912,790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Reporting Lab - Choose the Function for the Business Question</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hourly Rate</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hours Worked</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Formula Cell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Expected Function</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MA-101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Avery Chen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tidal North Kitchen sales</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SUMIFS</t>
+        </is>
+      </c>
+      <c r="J4">
+        <f>IF(H4="","Enter formula",IF(ABS(H4-SUMIFS('Raw Data'!H:H,'Raw Data'!D:D,"Kitchen",'Raw Data'!F:F,"North"))&lt;0.01,"Looks right","Check SUMIFS criteria"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MA-102</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Blake Ortiz</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Harborside open records</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COUNTIFS</t>
+        </is>
+      </c>
+      <c r="J5">
+        <f>IF(H5="","Enter formula",IF(H5=COUNTIFS('Raw Data'!A:A,"Harborside Medical Center",'Raw Data'!G:G,"Open"),"Looks right","Check COUNTIFS criteria"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MA-103</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Casey Patel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Meridian overtime flag for MA-103</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>IF</t>
+        </is>
+      </c>
+      <c r="J6">
+        <f>IF(H6="","Enter formula",IF(H6="Overtime","Looks right","IF should flag &gt;40 hours"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MA-104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Devon Reed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Last day of current month</t>
+        </is>
+      </c>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EOMONTH</t>
+        </is>
+      </c>
+      <c r="J7">
+        <f>IF(H7="","Enter formula",IF(H7=EOMONTH(TODAY(),0),"Looks right","Use EOMONTH(TODAY(),0)"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MA-105</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Emery Silva</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Text label: Company - Category - Region for first raw row</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TEXTJOIN</t>
+        </is>
+      </c>
+      <c r="J8">
+        <f>IF(H8="","Enter formula",IF(H8="Anchor &amp; Oak Events - Wedding - North","Looks right","Check TEXTJOIN delimiter and source cells"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lookup ID</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Student Formula</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Expected Function</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MA-103</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>XLOOKUP</t>
+        </is>
+      </c>
+      <c r="D11">
+        <f>IF(B11="","Enter formula",IF(B11="Casey Patel","Looks right","Check XLOOKUP lookup and return arrays"))</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SUMIFS total uses Raw Data Amount as sum range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MA-999</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>XLOOKUP with if_not_found</t>
+        </is>
+      </c>
+      <c r="D12">
+        <f>IF(B12="","Enter formula",IF(B12="Check ID","Looks right","Use if_not_found message: Check ID"))</f>
+        <v/>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>COUNTIFS counts rows meeting multiple conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IF should return Overtime when hours are greater than 40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TEXTJOIN should include delimiter and ignore blanks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Write formulas in the yellow Formula Cell references.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>EXCEL-M03-L01 - Class Challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Read each scenario, enter the needed inputs into the yellow cells, then put the final numeric answer in the blue cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Graded / Next-Level Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Input 1</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Input 2</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Input 3</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Input 4</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Input 5</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Input 6</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Final Answer</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Anchor &amp; Oak shows Jan-Jun revenue of $35,700, $21,400, $29,500, $43,300, $54,600, and $67,200. Enter each monthly revenue and calculate the total.</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
+      <c r="H7" s="39" t="n"/>
+      <c r="I7" s="29" t="n"/>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>Use SUM across all six input cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Using the same Jan-Jun revenue figures from row 1, calculate the average visible monthly revenue.</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="40" t="n"/>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Use AVERAGE across all six input cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Using the same Jan-Jun revenue figures, identify the highest visible monthly revenue.</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>Use MAX on the six revenue cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Using the same Jan-Jun revenue figures, identify the lowest visible monthly revenue.</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="39" t="n"/>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>Use MIN on the six revenue cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Using the same Jan-Jun revenue figures, calculate the spread between the highest and lowest visible month.</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>Subtract MIN from MAX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Using the same Jan-Jun revenue figures, count how many numeric revenue entries are visible.</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="33" t="n"/>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>Use COUNT on the numeric cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Tidal Goods shows sales rows: Kitchen North $8,400; Storage North $5,100; Kitchen South $3,900; Kitchen North $6,200. Calculate total Kitchen North sales.</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>Add the first and fourth sales amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Using the Tidal rows from row 7, calculate Kitchen North sales as a percent of all North-region sales.</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="41" t="n"/>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>Kitchen North divided by all North sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Harborside reports 17 late records across 4 departments. Calculate the average late records per department.</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="34" t="n"/>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>Divide late records by departments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Harborside reports 1 urgent pattern out of 17 late records. Calculate the urgent-pattern share.</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="41" t="n"/>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>Urgent patterns divided by late records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Harborside needs shift numbers 1 through 12. Calculate the sum of that generated sequence.</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="33" t="n"/>
+      <c r="J17" s="30" t="inlineStr">
+        <is>
+          <t>Use SEQUENCE or the formula n*(n+1)/2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Tidal Goods inventory shows Tote 20 units at $18, Mug 45 units at $7, and Apron 12 units at $22. Calculate total inventory value.</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>Multiply each quantity by its cost, then add.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Using the Tidal inventory data from row 12, calculate the highest single-item inventory value.</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="30" t="inlineStr">
+        <is>
+          <t>Find the largest quantity-times-cost product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Using the Tidal inventory data from row 12, calculate the Tote share of total inventory value.</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="41" t="n"/>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>Tote value divided by total inventory value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>The report output shows 13.746892 and should be rounded to 2 decimal places. Calculate the rounded result.</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="34" t="n"/>
+      <c r="J21" s="30" t="inlineStr">
+        <is>
+          <t>Use ROUND(number, digits).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.11000061035156" customWidth="1" min="1" max="1"/>
@@ -3712,7 +4734,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>=SUM(range)</t>
+          <t>'=SUM(range)</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
@@ -3734,7 +4756,7 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>=AVERAGE(range)</t>
+          <t>'=AVERAGE(range)</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
@@ -3756,7 +4778,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>=IF(test,value_if_true,value_if_false)</t>
+          <t>'=IF(test,value_if_true,value_if_false)</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
@@ -3778,7 +4800,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>=COUNTIFS(criteria_range,criteria)</t>
+          <t>'=COUNTIFS(criteria_range,criteria)</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -3800,7 +4822,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>=XLOOKUP(lookup_value,lookup_array,return_array)</t>
+          <t>'=XLOOKUP(lookup_value,lookup_array,return_array)</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -3822,7 +4844,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>=FILTER(array,include)</t>
+          <t>'=FILTER(array,include)</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -3836,19 +4858,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
